--- a/results/pooled_results_OR_multi_exposure_models_cold_parent.xlsx
+++ b/results/pooled_results_OR_multi_exposure_models_cold_parent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Keiji\Documents\Research\ahs_fibromyalgia\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7071F948-9209-459D-9E06-42CBB5FFA80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9EF47D-0E56-4AF4-9C9E-3300B4FE4F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{797B858C-DA94-466A-A931-46BE830858D9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="46">
   <si>
     <t>Cold parent</t>
   </si>
@@ -182,6 +182,12 @@
   </si>
   <si>
     <t>Stomach ulcer</t>
+  </si>
+  <si>
+    <t>Rheumatism</t>
+  </si>
+  <si>
+    <t>&lt;.0001</t>
   </si>
 </sst>
 </file>
@@ -329,6 +335,8 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -344,9 +352,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -682,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9215179F-2EFE-4E44-8C52-C38DCB1662E2}">
-  <dimension ref="B1:V50"/>
+  <dimension ref="B1:V54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" style="3" bestFit="1" customWidth="1"/>
@@ -723,30 +731,30 @@
       <c r="C4" s="5"/>
     </row>
     <row r="5" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="16"/>
-      <c r="I5" s="14" t="s">
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+      <c r="I5" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="16"/>
-      <c r="N5" s="14" t="s">
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="18"/>
+      <c r="N5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="16"/>
-      <c r="S5" s="14" t="s">
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="18"/>
+      <c r="S5" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="T5" s="15"/>
-      <c r="U5" s="15"/>
-      <c r="V5" s="16"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="18"/>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.3">
       <c r="D6" s="9"/>
@@ -821,87 +829,87 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="18"/>
+      <c r="E8" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="19"/>
+      <c r="G8" s="13"/>
       <c r="I8" s="1">
         <v>1</v>
       </c>
-      <c r="J8" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="18"/>
+      <c r="J8" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" s="19"/>
+      <c r="L8" s="13"/>
       <c r="N8" s="1">
         <v>1</v>
       </c>
-      <c r="O8" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="18"/>
+      <c r="O8" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="13"/>
       <c r="S8" s="1">
         <v>1</v>
       </c>
-      <c r="T8" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="U8" s="17"/>
-      <c r="V8" s="18"/>
+      <c r="T8" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="U8" s="19"/>
+      <c r="V8" s="13"/>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>1.1531905</v>
+        <v>1.0154078</v>
       </c>
       <c r="E9" s="1">
-        <v>0.74991600000000003</v>
+        <v>0.64829000000000003</v>
       </c>
       <c r="F9" s="1">
-        <v>1.7733296000000001</v>
-      </c>
-      <c r="G9" s="18">
-        <v>0.51609000000000005</v>
+        <v>1.590419</v>
+      </c>
+      <c r="G9" s="13">
+        <v>0.94672999999999996</v>
       </c>
       <c r="I9" s="1">
-        <v>1.2090396999999999</v>
+        <v>1.0652349999999999</v>
       </c>
       <c r="J9" s="1">
-        <v>0.78943790000000003</v>
+        <v>0.68329770000000001</v>
       </c>
       <c r="K9" s="1">
-        <v>1.8516683</v>
-      </c>
-      <c r="L9" s="18">
-        <v>0.38262000000000002</v>
+        <v>1.6606608</v>
+      </c>
+      <c r="L9" s="13">
+        <v>0.78020100000000003</v>
       </c>
       <c r="N9" s="1">
-        <v>1.2823575</v>
+        <v>1.1308762000000001</v>
       </c>
       <c r="O9" s="1">
-        <v>0.83665219999999996</v>
+        <v>0.72442779999999996</v>
       </c>
       <c r="P9" s="1">
-        <v>1.9655011</v>
-      </c>
-      <c r="Q9" s="18">
-        <v>0.253581</v>
+        <v>1.7653669999999999</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>0.58818999999999999</v>
       </c>
       <c r="S9" s="1">
-        <v>1.2439918999999999</v>
+        <v>1.1026206999999999</v>
       </c>
       <c r="T9" s="1">
-        <v>0.81307629999999997</v>
+        <v>0.70804999999999996</v>
       </c>
       <c r="U9" s="1">
-        <v>1.9032848</v>
-      </c>
-      <c r="V9" s="18">
-        <v>0.31417</v>
+        <v>1.7170714</v>
+      </c>
+      <c r="V9" s="13">
+        <v>0.66542999999999997</v>
       </c>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.3">
@@ -909,68 +917,68 @@
         <v>4</v>
       </c>
       <c r="D10" s="1">
-        <v>1.5067889000000001</v>
+        <v>1.2734098</v>
       </c>
       <c r="E10" s="1">
-        <v>0.78380349999999999</v>
+        <v>0.62794300000000003</v>
       </c>
       <c r="F10" s="1">
-        <v>2.8966607999999998</v>
-      </c>
-      <c r="G10" s="18">
-        <v>0.21879999999999999</v>
+        <v>2.5823559999999999</v>
+      </c>
+      <c r="G10" s="13">
+        <v>0.50268900000000005</v>
       </c>
       <c r="I10" s="1">
-        <v>1.5791219999999999</v>
+        <v>1.301059</v>
       </c>
       <c r="J10" s="1">
-        <v>0.82574550000000002</v>
+        <v>0.64544809999999997</v>
       </c>
       <c r="K10" s="1">
-        <v>3.0198485000000002</v>
-      </c>
-      <c r="L10" s="18">
-        <v>0.16716</v>
+        <v>2.6226036000000001</v>
+      </c>
+      <c r="L10" s="13">
+        <v>0.461677</v>
       </c>
       <c r="N10" s="1">
-        <v>1.6055831</v>
+        <v>1.3077502999999999</v>
       </c>
       <c r="O10" s="1">
-        <v>0.83836029999999995</v>
+        <v>0.64585879999999996</v>
       </c>
       <c r="P10" s="1">
-        <v>3.0749271999999999</v>
-      </c>
-      <c r="Q10" s="18">
-        <v>0.153174</v>
+        <v>2.6479640999999998</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>0.45588000000000001</v>
       </c>
       <c r="S10" s="1">
-        <v>1.6264689000000001</v>
+        <v>1.3423651999999999</v>
       </c>
       <c r="T10" s="1">
-        <v>0.85149059999999999</v>
+        <v>0.66523030000000005</v>
       </c>
       <c r="U10" s="1">
-        <v>3.1067881000000002</v>
-      </c>
-      <c r="V10" s="18">
-        <v>0.14066999999999999</v>
+        <v>2.7087528000000001</v>
+      </c>
+      <c r="V10" s="13">
+        <v>0.41094000000000003</v>
       </c>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G11" s="18"/>
+      <c r="G11" s="13"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-      <c r="L11" s="18"/>
+      <c r="L11" s="13"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
-      <c r="Q11" s="18"/>
+      <c r="Q11" s="13"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
-      <c r="V11" s="18"/>
+      <c r="V11" s="13"/>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
@@ -982,126 +990,126 @@
       <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="18"/>
+      <c r="E12" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="15"/>
+      <c r="G12" s="13"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="18"/>
+      <c r="L12" s="13"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
-      <c r="Q12" s="18"/>
+      <c r="Q12" s="13"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
-      <c r="V12" s="18"/>
+      <c r="V12" s="13"/>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C13" s="7">
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>1.2714846</v>
+        <v>1.1696678</v>
       </c>
       <c r="E13" s="1">
-        <v>0.76431910000000003</v>
+        <v>0.69953220000000005</v>
       </c>
       <c r="F13" s="1">
-        <v>2.1151806999999998</v>
-      </c>
-      <c r="G13" s="18">
-        <v>0.35432000000000002</v>
+        <v>1.955768</v>
+      </c>
+      <c r="G13" s="13">
+        <v>0.54979699999999998</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="18"/>
+      <c r="L13" s="13"/>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="18"/>
+      <c r="Q13" s="13"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
-      <c r="V13" s="18"/>
+      <c r="V13" s="13"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C14" s="7">
         <v>2</v>
       </c>
       <c r="D14" s="12">
-        <v>1.9673073999999999</v>
+        <v>1.8335817000000001</v>
       </c>
       <c r="E14" s="12">
-        <v>1.1743646999999999</v>
+        <v>1.0810373</v>
       </c>
       <c r="F14" s="12">
-        <v>3.2956528</v>
-      </c>
-      <c r="G14" s="20">
-        <v>1.018E-2</v>
+        <v>3.1099960000000002</v>
+      </c>
+      <c r="G14" s="14">
+        <v>2.4528999999999999E-2</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="18"/>
+      <c r="L14" s="13"/>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="Q14" s="18"/>
+      <c r="Q14" s="13"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
-      <c r="V14" s="18"/>
+      <c r="V14" s="13"/>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C15" s="7">
         <v>3</v>
       </c>
       <c r="D15" s="12">
-        <v>3.4556046</v>
+        <v>3.1552123000000001</v>
       </c>
       <c r="E15" s="12">
-        <v>1.8700288</v>
+        <v>1.6639439</v>
       </c>
       <c r="F15" s="12">
-        <v>6.3855715999999996</v>
-      </c>
-      <c r="G15" s="20">
-        <v>7.9200000000000001E-5</v>
+        <v>5.9829929999999996</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4.4499999999999997E-4</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="18"/>
+      <c r="L15" s="13"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="Q15" s="18"/>
+      <c r="Q15" s="13"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
-      <c r="V15" s="18"/>
+      <c r="V15" s="13"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C16" s="7"/>
-      <c r="G16" s="18"/>
+      <c r="G16" s="13"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="18"/>
+      <c r="L16" s="13"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="Q16" s="18"/>
+      <c r="Q16" s="13"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
-      <c r="V16" s="18"/>
+      <c r="V16" s="13"/>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
@@ -1110,91 +1118,91 @@
       <c r="C17" s="7">
         <v>0</v>
       </c>
-      <c r="G17" s="18"/>
+      <c r="G17" s="13"/>
       <c r="I17" s="1">
         <v>1</v>
       </c>
-      <c r="J17" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="K17" s="13"/>
-      <c r="L17" s="18"/>
+      <c r="J17" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17" s="15"/>
+      <c r="L17" s="13"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
-      <c r="Q17" s="18"/>
+      <c r="Q17" s="13"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
-      <c r="V17" s="18"/>
+      <c r="V17" s="13"/>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C18" s="7">
         <v>1</v>
       </c>
-      <c r="G18" s="18"/>
+      <c r="G18" s="13"/>
       <c r="I18" s="1">
-        <v>1.3327007</v>
+        <v>1.4481234999999999</v>
       </c>
       <c r="J18" s="1">
-        <v>0.86854929999999997</v>
+        <v>0.93032179999999998</v>
       </c>
       <c r="K18" s="1">
-        <v>2.0448940000000002</v>
-      </c>
-      <c r="L18" s="18">
-        <v>0.18847</v>
+        <v>2.2541251</v>
+      </c>
+      <c r="L18" s="13">
+        <v>0.100952</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
-      <c r="Q18" s="18"/>
+      <c r="Q18" s="13"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
-      <c r="V18" s="18"/>
+      <c r="V18" s="13"/>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C19" s="7">
         <v>2</v>
       </c>
-      <c r="G19" s="18"/>
-      <c r="I19" s="1">
-        <v>1.6825296999999999</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0.97264300000000004</v>
-      </c>
-      <c r="K19" s="1">
-        <v>2.9105297000000001</v>
-      </c>
-      <c r="L19" s="18">
-        <v>6.275E-2</v>
+      <c r="G19" s="13"/>
+      <c r="I19" s="12">
+        <v>1.85155</v>
+      </c>
+      <c r="J19" s="12">
+        <v>1.0598046999999999</v>
+      </c>
+      <c r="K19" s="12">
+        <v>3.2347823999999998</v>
+      </c>
+      <c r="L19" s="14">
+        <v>3.0487E-2</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
-      <c r="Q19" s="18"/>
+      <c r="Q19" s="13"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
-      <c r="V19" s="18"/>
+      <c r="V19" s="13"/>
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C20" s="7"/>
-      <c r="G20" s="18"/>
+      <c r="G20" s="13"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="18"/>
+      <c r="L20" s="13"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="18"/>
+      <c r="Q20" s="13"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
-      <c r="V20" s="18"/>
+      <c r="V20" s="13"/>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
@@ -1203,117 +1211,117 @@
       <c r="C21" s="7">
         <v>0</v>
       </c>
-      <c r="G21" s="18"/>
+      <c r="G21" s="13"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-      <c r="L21" s="18"/>
+      <c r="L21" s="13"/>
       <c r="N21" s="1">
         <v>1</v>
       </c>
-      <c r="O21" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="18"/>
+      <c r="O21" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="13"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
-      <c r="V21" s="18"/>
+      <c r="V21" s="13"/>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C22" s="7">
         <v>1</v>
       </c>
-      <c r="G22" s="18"/>
+      <c r="G22" s="13"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="18"/>
-      <c r="N22" s="12">
-        <v>1.9390855</v>
-      </c>
-      <c r="O22" s="12">
-        <v>1.0360876999999999</v>
-      </c>
-      <c r="P22" s="12">
-        <v>3.6290868999999999</v>
-      </c>
-      <c r="Q22" s="20">
-        <v>3.8400999999999998E-2</v>
+      <c r="L22" s="13"/>
+      <c r="N22" s="1">
+        <v>1.7689214</v>
+      </c>
+      <c r="O22" s="1">
+        <v>0.93933069999999996</v>
+      </c>
+      <c r="P22" s="1">
+        <v>3.3311837</v>
+      </c>
+      <c r="Q22" s="13">
+        <v>7.7310000000000004E-2</v>
       </c>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
-      <c r="V22" s="18"/>
+      <c r="V22" s="13"/>
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C23" s="7">
         <v>2</v>
       </c>
-      <c r="G23" s="18"/>
+      <c r="G23" s="13"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="18"/>
+      <c r="L23" s="13"/>
       <c r="N23" s="12">
-        <v>2.7010025999999998</v>
+        <v>2.534643</v>
       </c>
       <c r="O23" s="12">
-        <v>1.3708541999999999</v>
+        <v>1.3108481999999999</v>
       </c>
       <c r="P23" s="12">
-        <v>5.3218025000000004</v>
-      </c>
-      <c r="Q23" s="20">
-        <v>4.1549999999999998E-3</v>
+        <v>4.9009603000000004</v>
+      </c>
+      <c r="Q23" s="14">
+        <v>5.7299999999999999E-3</v>
       </c>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
-      <c r="V23" s="18"/>
+      <c r="V23" s="13"/>
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C24" s="7">
         <v>3</v>
       </c>
-      <c r="G24" s="18"/>
+      <c r="G24" s="13"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="18"/>
-      <c r="N24" s="12">
-        <v>3.0842154000000002</v>
-      </c>
-      <c r="O24" s="12">
-        <v>1.2090186000000001</v>
-      </c>
-      <c r="P24" s="12">
-        <v>7.8678562999999997</v>
-      </c>
-      <c r="Q24" s="20">
-        <v>1.847E-2</v>
+      <c r="L24" s="13"/>
+      <c r="N24" s="1">
+        <v>2.5289096999999998</v>
+      </c>
+      <c r="O24" s="1">
+        <v>0.95412750000000002</v>
+      </c>
+      <c r="P24" s="1">
+        <v>6.7028610999999998</v>
+      </c>
+      <c r="Q24" s="13">
+        <v>6.2089999999999999E-2</v>
       </c>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
-      <c r="V24" s="18"/>
+      <c r="V24" s="13"/>
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C25" s="7"/>
-      <c r="G25" s="18"/>
+      <c r="G25" s="13"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="18"/>
+      <c r="L25" s="13"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
-      <c r="Q25" s="18"/>
+      <c r="Q25" s="13"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
-      <c r="V25" s="18"/>
+      <c r="V25" s="13"/>
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
@@ -1322,255 +1330,255 @@
       <c r="C26" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G26" s="18"/>
+      <c r="G26" s="13"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-      <c r="L26" s="18"/>
+      <c r="L26" s="13"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
-      <c r="Q26" s="18"/>
+      <c r="Q26" s="13"/>
       <c r="S26" s="1">
         <v>1</v>
       </c>
-      <c r="T26" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="U26" s="13"/>
-      <c r="V26" s="18"/>
+      <c r="T26" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="U26" s="15"/>
+      <c r="V26" s="13"/>
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G27" s="18"/>
+      <c r="G27" s="13"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
-      <c r="L27" s="18"/>
+      <c r="L27" s="13"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
-      <c r="Q27" s="18"/>
+      <c r="Q27" s="13"/>
       <c r="S27" s="1">
-        <v>0.90028350000000001</v>
+        <v>0.93304310000000001</v>
       </c>
       <c r="T27" s="1">
-        <v>0.50191870000000005</v>
+        <v>0.51131649999999995</v>
       </c>
       <c r="U27" s="1">
-        <v>1.6148241999999999</v>
-      </c>
-      <c r="V27" s="18">
-        <v>0.72431999999999996</v>
+        <v>1.7026037000000001</v>
+      </c>
+      <c r="V27" s="13">
+        <v>0.82113000000000003</v>
       </c>
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G28" s="18"/>
+      <c r="G28" s="13"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
-      <c r="L28" s="18"/>
+      <c r="L28" s="13"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
-      <c r="Q28" s="18"/>
+      <c r="Q28" s="13"/>
       <c r="S28" s="1">
-        <v>1.1691826999999999</v>
+        <v>1.1997346</v>
       </c>
       <c r="T28" s="1">
-        <v>0.68683209999999995</v>
+        <v>0.70015360000000004</v>
       </c>
       <c r="U28" s="1">
-        <v>1.9902801999999999</v>
-      </c>
-      <c r="V28" s="18">
-        <v>0.56437000000000004</v>
+        <v>2.0557818999999999</v>
+      </c>
+      <c r="V28" s="13">
+        <v>0.50731999999999999</v>
       </c>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C29" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G29" s="18"/>
+      <c r="G29" s="13"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-      <c r="L29" s="18"/>
+      <c r="L29" s="13"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
-      <c r="Q29" s="18"/>
+      <c r="Q29" s="13"/>
       <c r="S29" s="1">
-        <v>1.1347563000000001</v>
+        <v>0.95858739999999998</v>
       </c>
       <c r="T29" s="1">
-        <v>0.63781169999999998</v>
+        <v>0.51544279999999998</v>
       </c>
       <c r="U29" s="1">
-        <v>2.0188902999999998</v>
-      </c>
-      <c r="V29" s="18">
-        <v>0.66683000000000003</v>
+        <v>1.7827191</v>
+      </c>
+      <c r="V29" s="13">
+        <v>0.89359999999999995</v>
       </c>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G30" s="18"/>
+      <c r="G30" s="13"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="18"/>
+      <c r="L30" s="13"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-      <c r="Q30" s="18"/>
+      <c r="Q30" s="13"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
-      <c r="V30" s="18"/>
+      <c r="V30" s="13"/>
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B31" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D31" s="12">
-        <v>0.97001839999999995</v>
+        <v>0.96114999999999995</v>
       </c>
       <c r="E31" s="12">
-        <v>0.95128210000000002</v>
+        <v>0.94072069999999997</v>
       </c>
       <c r="F31" s="12">
-        <v>0.98912370000000005</v>
-      </c>
-      <c r="G31" s="20">
-        <v>2.2300000000000002E-3</v>
+        <v>0.98202299999999998</v>
+      </c>
+      <c r="G31" s="14">
+        <v>3.0400000000000002E-4</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="12">
-        <v>0.97224889999999997</v>
+        <v>0.96370020000000001</v>
       </c>
       <c r="J31" s="12">
-        <v>0.95343999999999995</v>
+        <v>0.94309189999999998</v>
       </c>
       <c r="K31" s="12">
-        <v>0.99142889999999995</v>
-      </c>
-      <c r="L31" s="20">
-        <v>4.7600000000000003E-3</v>
+        <v>0.98475889999999999</v>
+      </c>
+      <c r="L31" s="14">
+        <v>8.0900000000000004E-4</v>
       </c>
       <c r="M31" s="3"/>
       <c r="N31" s="12">
-        <v>0.96706890000000001</v>
+        <v>0.95809469999999997</v>
       </c>
       <c r="O31" s="12">
-        <v>0.94854950000000005</v>
+        <v>0.93781990000000004</v>
       </c>
       <c r="P31" s="12">
-        <v>0.98594979999999999</v>
-      </c>
-      <c r="Q31" s="20">
-        <v>6.9399999999999996E-4</v>
+        <v>0.97880780000000001</v>
+      </c>
+      <c r="Q31" s="14">
+        <v>8.92E-5</v>
       </c>
       <c r="R31" s="3"/>
       <c r="S31" s="12">
-        <v>0.96993320000000005</v>
+        <v>0.96072210000000002</v>
       </c>
       <c r="T31" s="12">
-        <v>0.95138029999999996</v>
+        <v>0.94041819999999998</v>
       </c>
       <c r="U31" s="12">
-        <v>0.9888479</v>
-      </c>
-      <c r="V31" s="20">
-        <v>1.9599999999999999E-3</v>
+        <v>0.98146440000000001</v>
+      </c>
+      <c r="V31" s="14">
+        <v>2.4000000000000001E-4</v>
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G32" s="18"/>
+      <c r="G32" s="13"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
-      <c r="L32" s="18"/>
+      <c r="L32" s="13"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
-      <c r="Q32" s="18"/>
+      <c r="Q32" s="13"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
       <c r="U32" s="1"/>
-      <c r="V32" s="18"/>
+      <c r="V32" s="13"/>
     </row>
     <row r="33" spans="2:22" ht="16.2" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D33" s="1">
-        <v>0.96086870000000002</v>
+        <v>0.94940349999999996</v>
       </c>
       <c r="E33" s="1">
-        <v>0.91268499999999997</v>
+        <v>0.89823039999999998</v>
       </c>
       <c r="F33" s="1">
-        <v>1.0115959999999999</v>
-      </c>
-      <c r="G33" s="18">
-        <v>0.12823999999999999</v>
+        <v>1.0034920000000001</v>
+      </c>
+      <c r="G33" s="13">
+        <v>6.6216999999999998E-2</v>
       </c>
       <c r="I33" s="1">
-        <v>0.96620150000000005</v>
+        <v>0.95430939999999997</v>
       </c>
       <c r="J33" s="1">
-        <v>0.91780680000000003</v>
+        <v>0.90312939999999997</v>
       </c>
       <c r="K33" s="1">
-        <v>1.0171479999999999</v>
-      </c>
-      <c r="L33" s="18">
-        <v>0.18956000000000001</v>
+        <v>1.0083896999999999</v>
+      </c>
+      <c r="L33" s="13">
+        <v>9.6213999999999994E-2</v>
       </c>
       <c r="N33" s="1">
-        <v>0.96507069999999995</v>
+        <v>0.9538354</v>
       </c>
       <c r="O33" s="1">
-        <v>0.91610539999999996</v>
+        <v>0.90221779999999996</v>
       </c>
       <c r="P33" s="1">
-        <v>1.0166531999999999</v>
-      </c>
-      <c r="Q33" s="18">
-        <v>0.180645</v>
+        <v>1.0084062</v>
+      </c>
+      <c r="Q33" s="13">
+        <v>9.5769999999999994E-2</v>
       </c>
       <c r="S33" s="1">
-        <v>0.96815079999999998</v>
+        <v>0.95639439999999998</v>
       </c>
       <c r="T33" s="1">
-        <v>0.9196725</v>
+        <v>0.90442929999999999</v>
       </c>
       <c r="U33" s="1">
-        <v>1.0191846</v>
-      </c>
-      <c r="V33" s="18">
-        <v>0.2167</v>
+        <v>1.0113452000000001</v>
+      </c>
+      <c r="V33" s="13">
+        <v>0.11756999999999999</v>
       </c>
     </row>
     <row r="34" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G34" s="18"/>
+      <c r="G34" s="13"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="18"/>
+      <c r="L34" s="13"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="18"/>
+      <c r="Q34" s="13"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
       <c r="U34" s="1"/>
-      <c r="V34" s="18"/>
+      <c r="V34" s="13"/>
     </row>
     <row r="35" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B35" s="3" t="s">
@@ -1582,87 +1590,87 @@
       <c r="D35" s="1">
         <v>1</v>
       </c>
-      <c r="E35" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F35" s="13"/>
-      <c r="G35" s="18"/>
+      <c r="E35" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" s="15"/>
+      <c r="G35" s="13"/>
       <c r="I35" s="1">
         <v>1</v>
       </c>
-      <c r="J35" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="K35" s="13"/>
-      <c r="L35" s="18"/>
+      <c r="J35" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="K35" s="15"/>
+      <c r="L35" s="13"/>
       <c r="N35" s="1">
         <v>1</v>
       </c>
-      <c r="O35" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="P35" s="13"/>
-      <c r="Q35" s="18"/>
+      <c r="O35" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="13"/>
       <c r="S35" s="1">
         <v>1</v>
       </c>
-      <c r="T35" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="U35" s="13"/>
-      <c r="V35" s="18"/>
+      <c r="T35" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="U35" s="15"/>
+      <c r="V35" s="13"/>
     </row>
     <row r="36" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C36" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D36" s="1">
-        <v>1.5533992999999999</v>
+        <v>1.5135406</v>
       </c>
       <c r="E36" s="1">
-        <v>0.89758490000000002</v>
+        <v>0.86315710000000001</v>
       </c>
       <c r="F36" s="1">
-        <v>2.6883802999999999</v>
-      </c>
-      <c r="G36" s="18">
-        <v>0.11545999999999999</v>
+        <v>2.6539839999999999</v>
+      </c>
+      <c r="G36" s="13">
+        <v>0.14799499999999999</v>
       </c>
       <c r="I36" s="1">
-        <v>1.4247299</v>
+        <v>1.3835222</v>
       </c>
       <c r="J36" s="1">
-        <v>0.82800189999999996</v>
+        <v>0.79497470000000003</v>
       </c>
       <c r="K36" s="1">
-        <v>2.4515102</v>
-      </c>
-      <c r="L36" s="18">
-        <v>0.20102</v>
+        <v>2.4077918</v>
+      </c>
+      <c r="L36" s="13">
+        <v>0.25070999999999999</v>
       </c>
       <c r="N36" s="1">
-        <v>1.5203807</v>
+        <v>1.4634422</v>
       </c>
       <c r="O36" s="1">
-        <v>0.88313719999999996</v>
+        <v>0.83963569999999998</v>
       </c>
       <c r="P36" s="1">
-        <v>2.6174384000000002</v>
-      </c>
-      <c r="Q36" s="18">
-        <v>0.130575</v>
+        <v>2.5507049999999998</v>
+      </c>
+      <c r="Q36" s="13">
+        <v>0.17907000000000001</v>
       </c>
       <c r="S36" s="1">
-        <v>1.4171370999999999</v>
+        <v>1.3758946999999999</v>
       </c>
       <c r="T36" s="1">
-        <v>0.82377409999999995</v>
+        <v>0.79115270000000004</v>
       </c>
       <c r="U36" s="1">
-        <v>2.4378983999999999</v>
-      </c>
-      <c r="V36" s="18">
-        <v>0.20771000000000001</v>
+        <v>2.3928202000000001</v>
+      </c>
+      <c r="V36" s="13">
+        <v>0.25825999999999999</v>
       </c>
     </row>
     <row r="37" spans="2:22" x14ac:dyDescent="0.3">
@@ -1670,68 +1678,68 @@
         <v>6</v>
       </c>
       <c r="D37" s="1">
-        <v>1.6088126</v>
+        <v>1.5866453</v>
       </c>
       <c r="E37" s="1">
-        <v>0.86354249999999999</v>
+        <v>0.84039359999999996</v>
       </c>
       <c r="F37" s="1">
-        <v>2.9972794</v>
-      </c>
-      <c r="G37" s="18">
-        <v>0.1341</v>
+        <v>2.9955530000000001</v>
+      </c>
+      <c r="G37" s="13">
+        <v>0.15446199999999999</v>
       </c>
       <c r="I37" s="1">
-        <v>1.3445537000000001</v>
+        <v>1.3325009000000001</v>
       </c>
       <c r="J37" s="1">
-        <v>0.73021899999999995</v>
+        <v>0.71522110000000005</v>
       </c>
       <c r="K37" s="1">
-        <v>2.4757291000000001</v>
-      </c>
-      <c r="L37" s="18">
-        <v>0.34166000000000002</v>
+        <v>2.4825311999999999</v>
+      </c>
+      <c r="L37" s="13">
+        <v>0.36573600000000001</v>
       </c>
       <c r="N37" s="1">
-        <v>1.6075653000000001</v>
+        <v>1.5488678</v>
       </c>
       <c r="O37" s="1">
-        <v>0.86818079999999997</v>
+        <v>0.82512459999999999</v>
       </c>
       <c r="P37" s="1">
-        <v>2.9766452999999999</v>
-      </c>
-      <c r="Q37" s="18">
-        <v>0.13090599999999999</v>
+        <v>2.9074293</v>
+      </c>
+      <c r="Q37" s="13">
+        <v>0.17319999999999999</v>
       </c>
       <c r="S37" s="1">
-        <v>1.3157939000000001</v>
+        <v>1.3164336999999999</v>
       </c>
       <c r="T37" s="1">
-        <v>0.71258710000000003</v>
+        <v>0.70420329999999998</v>
       </c>
       <c r="U37" s="1">
-        <v>2.4296169000000001</v>
-      </c>
-      <c r="V37" s="18">
-        <v>0.38027</v>
+        <v>2.4609336000000002</v>
+      </c>
+      <c r="V37" s="13">
+        <v>0.38891999999999999</v>
       </c>
     </row>
     <row r="38" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G38" s="18"/>
+      <c r="G38" s="13"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="18"/>
+      <c r="L38" s="13"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
-      <c r="Q38" s="18"/>
+      <c r="Q38" s="13"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
-      <c r="V38" s="18"/>
+      <c r="V38" s="13"/>
     </row>
     <row r="39" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B39" s="3" t="s">
@@ -1743,103 +1751,103 @@
       <c r="D39" s="1">
         <v>1</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F39" s="13"/>
-      <c r="G39" s="18"/>
+      <c r="E39" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39" s="15"/>
+      <c r="G39" s="13"/>
       <c r="I39" s="1">
         <v>1</v>
       </c>
-      <c r="J39" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="K39" s="13"/>
-      <c r="L39" s="18"/>
+      <c r="J39" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="K39" s="15"/>
+      <c r="L39" s="13"/>
       <c r="N39" s="1">
         <v>1</v>
       </c>
-      <c r="O39" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="P39" s="13"/>
-      <c r="Q39" s="18"/>
+      <c r="O39" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="13"/>
       <c r="S39" s="1">
         <v>1</v>
       </c>
-      <c r="T39" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="U39" s="13"/>
-      <c r="V39" s="18"/>
+      <c r="T39" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="U39" s="15"/>
+      <c r="V39" s="13"/>
     </row>
     <row r="40" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C40" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="1">
-        <v>0.80460920000000002</v>
+        <v>0.7892787</v>
       </c>
       <c r="E40" s="1">
-        <v>0.52916010000000002</v>
+        <v>0.52290829999999999</v>
       </c>
       <c r="F40" s="1">
-        <v>1.2234406</v>
-      </c>
-      <c r="G40" s="18">
-        <v>0.30861</v>
+        <v>1.1913389999999999</v>
+      </c>
+      <c r="G40" s="13">
+        <v>0.25980199999999998</v>
       </c>
       <c r="I40" s="1">
-        <v>0.84526029999999996</v>
+        <v>0.82924189999999998</v>
       </c>
       <c r="J40" s="1">
-        <v>0.55743909999999997</v>
+        <v>0.55013239999999997</v>
       </c>
       <c r="K40" s="1">
-        <v>1.2816917000000001</v>
-      </c>
-      <c r="L40" s="18">
-        <v>0.42793999999999999</v>
+        <v>1.2499574</v>
+      </c>
+      <c r="L40" s="13">
+        <v>0.37095499999999998</v>
       </c>
       <c r="N40" s="1">
-        <v>0.85625150000000005</v>
+        <v>0.84274249999999995</v>
       </c>
       <c r="O40" s="1">
-        <v>0.56594679999999997</v>
+        <v>0.55890200000000001</v>
       </c>
       <c r="P40" s="1">
-        <v>1.2954692000000001</v>
-      </c>
-      <c r="Q40" s="18">
-        <v>0.46196900000000002</v>
+        <v>1.2707325</v>
+      </c>
+      <c r="Q40" s="13">
+        <v>0.41399999999999998</v>
       </c>
       <c r="S40" s="1">
-        <v>0.8481303</v>
+        <v>0.84303519999999998</v>
       </c>
       <c r="T40" s="1">
-        <v>0.55832190000000004</v>
+        <v>0.55788280000000001</v>
       </c>
       <c r="U40" s="1">
-        <v>1.2883697000000001</v>
-      </c>
-      <c r="V40" s="18">
-        <v>0.43928</v>
+        <v>1.2739385999999999</v>
+      </c>
+      <c r="V40" s="13">
+        <v>0.41738999999999998</v>
       </c>
     </row>
     <row r="41" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G41" s="18"/>
+      <c r="G41" s="13"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="18"/>
+      <c r="L41" s="13"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
-      <c r="Q41" s="18"/>
+      <c r="Q41" s="13"/>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
-      <c r="V41" s="18"/>
+      <c r="V41" s="13"/>
     </row>
     <row r="42" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
@@ -1851,157 +1859,156 @@
       <c r="D42" s="1">
         <v>1</v>
       </c>
-      <c r="E42" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F42" s="13"/>
-      <c r="G42" s="18"/>
+      <c r="E42" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" s="15"/>
+      <c r="G42" s="13"/>
       <c r="I42" s="1">
         <v>1</v>
       </c>
-      <c r="J42" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="K42" s="13"/>
-      <c r="L42" s="18"/>
+      <c r="J42" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="K42" s="15"/>
+      <c r="L42" s="13"/>
       <c r="N42" s="1">
         <v>1</v>
       </c>
-      <c r="O42" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="P42" s="13"/>
-      <c r="Q42" s="18"/>
+      <c r="O42" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="P42" s="15"/>
+      <c r="Q42" s="13"/>
       <c r="S42" s="1">
         <v>1</v>
       </c>
-      <c r="T42" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="U42" s="13"/>
-      <c r="V42" s="18"/>
+      <c r="T42" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="U42" s="15"/>
+      <c r="V42" s="13"/>
     </row>
     <row r="43" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C43" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D43" s="1">
-        <v>1.3312046</v>
+        <v>1.2368147</v>
       </c>
       <c r="E43" s="1">
-        <v>0.55544130000000003</v>
+        <v>0.51289549999999995</v>
       </c>
       <c r="F43" s="1">
-        <v>3.1904463000000001</v>
-      </c>
-      <c r="G43" s="18">
-        <v>0.52107000000000003</v>
+        <v>2.9824999999999999</v>
+      </c>
+      <c r="G43" s="13">
+        <v>0.63590999999999998</v>
       </c>
       <c r="I43" s="1">
-        <v>1.2394658999999999</v>
+        <v>1.1647414</v>
       </c>
       <c r="J43" s="1">
-        <v>0.51850479999999999</v>
+        <v>0.48387750000000002</v>
       </c>
       <c r="K43" s="1">
-        <v>2.9628958999999999</v>
-      </c>
-      <c r="L43" s="18">
-        <v>0.62912000000000001</v>
+        <v>2.8036487000000001</v>
+      </c>
+      <c r="L43" s="13">
+        <v>0.73356500000000002</v>
       </c>
       <c r="N43" s="1">
-        <v>1.2427600000000001</v>
+        <v>1.202099</v>
       </c>
       <c r="O43" s="1">
-        <v>0.51992539999999998</v>
+        <v>0.49883490000000003</v>
       </c>
       <c r="P43" s="1">
-        <v>2.9705271</v>
-      </c>
-      <c r="Q43" s="18">
-        <v>0.62485000000000002</v>
+        <v>2.8968340000000001</v>
+      </c>
+      <c r="Q43" s="13">
+        <v>0.68157000000000001</v>
       </c>
       <c r="S43" s="1">
-        <v>1.1761022999999999</v>
+        <v>1.1496461</v>
       </c>
       <c r="T43" s="1">
-        <v>0.49129919999999999</v>
+        <v>0.47644540000000002</v>
       </c>
       <c r="U43" s="1">
-        <v>2.8154260999999998</v>
-      </c>
-      <c r="V43" s="18">
-        <v>0.71560999999999997</v>
+        <v>2.7740558000000002</v>
+      </c>
+      <c r="V43" s="13">
+        <v>0.75624999999999998</v>
       </c>
     </row>
     <row r="44" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="B44" s="19"/>
-      <c r="C44" s="19" t="s">
+      <c r="C44" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D44" s="1">
-        <v>1.7982442000000001</v>
+        <v>1.8277543999999999</v>
       </c>
       <c r="E44" s="1">
-        <v>0.65181630000000002</v>
+        <v>0.65323739999999997</v>
       </c>
       <c r="F44" s="1">
-        <v>4.9610329999999996</v>
-      </c>
-      <c r="G44" s="18">
-        <v>0.25696000000000002</v>
+        <v>5.1140460000000001</v>
+      </c>
+      <c r="G44" s="13">
+        <v>0.25050899999999998</v>
       </c>
       <c r="I44" s="1">
-        <v>1.8638870000000001</v>
+        <v>1.9154758000000001</v>
       </c>
       <c r="J44" s="1">
-        <v>0.67746309999999998</v>
+        <v>0.68571369999999998</v>
       </c>
       <c r="K44" s="1">
-        <v>5.1280650999999997</v>
-      </c>
-      <c r="L44" s="18">
-        <v>0.22777</v>
+        <v>5.3506989999999996</v>
+      </c>
+      <c r="L44" s="13">
+        <v>0.214832</v>
       </c>
       <c r="N44" s="1">
-        <v>1.902209</v>
+        <v>2.0109256000000002</v>
       </c>
       <c r="O44" s="1">
-        <v>0.690465</v>
+        <v>0.71856200000000003</v>
       </c>
       <c r="P44" s="1">
-        <v>5.2405252999999998</v>
-      </c>
-      <c r="Q44" s="18">
-        <v>0.21354500000000001</v>
+        <v>5.6276583000000002</v>
+      </c>
+      <c r="Q44" s="13">
+        <v>0.18326000000000001</v>
       </c>
       <c r="S44" s="1">
-        <v>1.7831170000000001</v>
+        <v>1.9021036</v>
       </c>
       <c r="T44" s="1">
-        <v>0.64745490000000006</v>
+        <v>0.68073649999999997</v>
       </c>
       <c r="U44" s="1">
-        <v>4.9107767999999998</v>
-      </c>
-      <c r="V44" s="18">
-        <v>0.26305000000000001</v>
+        <v>5.3148289000000002</v>
+      </c>
+      <c r="V44" s="13">
+        <v>0.21994</v>
       </c>
     </row>
     <row r="45" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G45" s="18"/>
+      <c r="G45" s="13"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
-      <c r="L45" s="18"/>
+      <c r="L45" s="13"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
-      <c r="Q45" s="18"/>
+      <c r="Q45" s="13"/>
       <c r="S45" s="1"/>
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
-      <c r="V45" s="18"/>
+      <c r="V45" s="13"/>
     </row>
     <row r="46" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B46" s="3" t="s">
@@ -2013,106 +2020,106 @@
       <c r="D46" s="1">
         <v>1</v>
       </c>
-      <c r="E46" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F46" s="13"/>
-      <c r="G46" s="18"/>
+      <c r="E46" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" s="15"/>
+      <c r="G46" s="13"/>
       <c r="I46" s="1">
         <v>1</v>
       </c>
-      <c r="J46" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="K46" s="13"/>
-      <c r="L46" s="18"/>
+      <c r="J46" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="K46" s="15"/>
+      <c r="L46" s="13"/>
       <c r="N46" s="1">
         <v>1</v>
       </c>
-      <c r="O46" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="P46" s="13"/>
-      <c r="Q46" s="18"/>
+      <c r="O46" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="P46" s="15"/>
+      <c r="Q46" s="13"/>
       <c r="S46" s="1">
         <v>1</v>
       </c>
-      <c r="T46" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="U46" s="13"/>
-      <c r="V46" s="18"/>
+      <c r="T46" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="U46" s="15"/>
+      <c r="V46" s="13"/>
     </row>
     <row r="47" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C47" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D47" s="12">
-        <v>2.1084051000000001</v>
+        <v>1.9970751</v>
       </c>
       <c r="E47" s="12">
-        <v>1.2403141</v>
+        <v>1.1440929</v>
       </c>
       <c r="F47" s="12">
-        <v>3.5840697000000001</v>
-      </c>
-      <c r="G47" s="20">
-        <v>5.8799999999999998E-3</v>
+        <v>3.4860009999999999</v>
+      </c>
+      <c r="G47" s="14">
+        <v>1.4977000000000001E-2</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="12">
-        <v>2.0716199999999998</v>
+        <v>1.9507197999999999</v>
       </c>
       <c r="J47" s="12">
-        <v>1.2248635000000001</v>
+        <v>1.1196233</v>
       </c>
       <c r="K47" s="12">
-        <v>3.5037449999999999</v>
-      </c>
-      <c r="L47" s="20">
-        <v>6.62E-3</v>
+        <v>3.3987390999999998</v>
+      </c>
+      <c r="L47" s="14">
+        <v>1.8360999999999999E-2</v>
       </c>
       <c r="M47" s="3"/>
       <c r="N47" s="12">
-        <v>2.1091403999999998</v>
+        <v>1.9899879</v>
       </c>
       <c r="O47" s="12">
-        <v>1.2454775</v>
+        <v>1.1423479999999999</v>
       </c>
       <c r="P47" s="12">
-        <v>3.5717010999999999</v>
-      </c>
-      <c r="Q47" s="20">
-        <v>5.5120000000000004E-3</v>
+        <v>3.4665895999999998</v>
+      </c>
+      <c r="Q47" s="14">
+        <v>1.5129999999999999E-2</v>
       </c>
       <c r="R47" s="3"/>
       <c r="S47" s="12">
-        <v>2.0987364999999998</v>
+        <v>1.9534167</v>
       </c>
       <c r="T47" s="12">
-        <v>1.2403781</v>
+        <v>1.1218140999999999</v>
       </c>
       <c r="U47" s="12">
-        <v>3.5510906000000002</v>
-      </c>
-      <c r="V47" s="20">
-        <v>5.7499999999999999E-3</v>
+        <v>3.4014877000000001</v>
+      </c>
+      <c r="V47" s="14">
+        <v>1.7999999999999999E-2</v>
       </c>
     </row>
     <row r="48" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="G48" s="18"/>
+      <c r="G48" s="13"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-      <c r="L48" s="18"/>
+      <c r="L48" s="13"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
-      <c r="Q48" s="18"/>
+      <c r="Q48" s="13"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
-      <c r="V48" s="18"/>
+      <c r="V48" s="13"/>
     </row>
     <row r="49" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B49" s="3" t="s">
@@ -2124,93 +2131,211 @@
       <c r="D49" s="1">
         <v>1</v>
       </c>
-      <c r="E49" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F49" s="13"/>
-      <c r="G49" s="18"/>
+      <c r="E49" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F49" s="15"/>
+      <c r="G49" s="13"/>
       <c r="I49" s="1">
         <v>1</v>
       </c>
-      <c r="J49" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="K49" s="13"/>
-      <c r="L49" s="18"/>
+      <c r="J49" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="K49" s="15"/>
+      <c r="L49" s="13"/>
       <c r="N49" s="1">
         <v>1</v>
       </c>
-      <c r="O49" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="18"/>
+      <c r="O49" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="13"/>
       <c r="S49" s="1">
         <v>1</v>
       </c>
-      <c r="T49" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="U49" s="13"/>
-      <c r="V49" s="18"/>
+      <c r="T49" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="U49" s="15"/>
+      <c r="V49" s="13"/>
     </row>
     <row r="50" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C50" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="1">
-        <v>1.7877514000000001</v>
+        <v>1.5801118999999999</v>
       </c>
       <c r="E50" s="1">
-        <v>0.97043550000000001</v>
+        <v>0.8434488</v>
       </c>
       <c r="F50" s="1">
-        <v>3.2934234</v>
-      </c>
-      <c r="G50" s="18">
-        <v>6.234E-2</v>
-      </c>
-      <c r="I50" s="12">
-        <v>1.8767811000000001</v>
-      </c>
-      <c r="J50" s="12">
-        <v>1.0234065999999999</v>
-      </c>
-      <c r="K50" s="12">
-        <v>3.4417475</v>
-      </c>
-      <c r="L50" s="20">
-        <v>4.1889999999999997E-2</v>
-      </c>
-      <c r="M50" s="3"/>
-      <c r="N50" s="12">
-        <v>1.8509182</v>
-      </c>
-      <c r="O50" s="12">
-        <v>1.0047352000000001</v>
-      </c>
-      <c r="P50" s="12">
-        <v>3.4097523999999999</v>
-      </c>
-      <c r="Q50" s="20">
-        <v>4.8258000000000002E-2</v>
-      </c>
-      <c r="R50" s="3"/>
-      <c r="S50" s="12">
-        <v>1.8559623000000001</v>
-      </c>
-      <c r="T50" s="12">
-        <v>1.0092759</v>
-      </c>
-      <c r="U50" s="12">
-        <v>3.4129377999999999</v>
-      </c>
-      <c r="V50" s="20">
-        <v>4.6629999999999998E-2</v>
-      </c>
-    </row>
+        <v>2.960172</v>
+      </c>
+      <c r="G50" s="13">
+        <v>0.15307599999999999</v>
+      </c>
+      <c r="I50" s="1">
+        <v>1.6323823</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0.87246630000000003</v>
+      </c>
+      <c r="K50" s="1">
+        <v>3.0541833</v>
+      </c>
+      <c r="L50" s="13">
+        <v>0.125163</v>
+      </c>
+      <c r="N50" s="1">
+        <v>1.6441596999999999</v>
+      </c>
+      <c r="O50" s="1">
+        <v>0.87742989999999998</v>
+      </c>
+      <c r="P50" s="1">
+        <v>3.0808855999999998</v>
+      </c>
+      <c r="Q50" s="13">
+        <v>0.12060999999999999</v>
+      </c>
+      <c r="S50" s="1">
+        <v>1.6700841</v>
+      </c>
+      <c r="T50" s="1">
+        <v>0.8926598</v>
+      </c>
+      <c r="U50" s="1">
+        <v>3.1245731000000001</v>
+      </c>
+      <c r="V50" s="13">
+        <v>0.10849</v>
+      </c>
+    </row>
+    <row r="51" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="G51" s="13"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="13"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="13"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="13"/>
+    </row>
+    <row r="52" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1</v>
+      </c>
+      <c r="E52" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F52" s="15"/>
+      <c r="G52" s="13"/>
+      <c r="I52" s="1">
+        <v>1</v>
+      </c>
+      <c r="J52" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="K52" s="15"/>
+      <c r="L52" s="13"/>
+      <c r="N52" s="1">
+        <v>1</v>
+      </c>
+      <c r="O52" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="P52" s="15"/>
+      <c r="Q52" s="13"/>
+      <c r="S52" s="1">
+        <v>1</v>
+      </c>
+      <c r="T52" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="U52" s="15"/>
+      <c r="V52" s="13"/>
+    </row>
+    <row r="53" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="4"/>
+      <c r="C53" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="10">
+        <v>2.9927337000000001</v>
+      </c>
+      <c r="E53" s="10">
+        <v>1.8662201</v>
+      </c>
+      <c r="F53" s="10">
+        <v>4.7992489999999997</v>
+      </c>
+      <c r="G53" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H53" s="4"/>
+      <c r="I53" s="10">
+        <v>3.1075957000000001</v>
+      </c>
+      <c r="J53" s="10">
+        <v>1.9439854999999999</v>
+      </c>
+      <c r="K53" s="10">
+        <v>4.9677072999999998</v>
+      </c>
+      <c r="L53" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M53" s="4"/>
+      <c r="N53" s="10">
+        <v>3.0664201000000002</v>
+      </c>
+      <c r="O53" s="10">
+        <v>1.9190748</v>
+      </c>
+      <c r="P53" s="10">
+        <v>4.8997216000000003</v>
+      </c>
+      <c r="Q53" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="R53" s="4"/>
+      <c r="S53" s="10">
+        <v>3.0920941000000002</v>
+      </c>
+      <c r="T53" s="10">
+        <v>1.932064</v>
+      </c>
+      <c r="U53" s="10">
+        <v>4.9486175000000001</v>
+      </c>
+      <c r="V53" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="2:22" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="36">
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="O52:P52"/>
+    <mergeCell ref="T52:U52"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="T42:U42"/>
     <mergeCell ref="E46:F46"/>
     <mergeCell ref="J46:K46"/>
     <mergeCell ref="O46:P46"/>
@@ -2219,22 +2344,17 @@
     <mergeCell ref="J49:K49"/>
     <mergeCell ref="O49:P49"/>
     <mergeCell ref="T49:U49"/>
-    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="N5:Q5"/>
+    <mergeCell ref="S5:V5"/>
+    <mergeCell ref="O21:P21"/>
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="O8:P8"/>
     <mergeCell ref="T8:U8"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="J17:K17"/>
-    <mergeCell ref="T39:U39"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="T42:U42"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="N5:Q5"/>
-    <mergeCell ref="S5:V5"/>
-    <mergeCell ref="O21:P21"/>
     <mergeCell ref="T26:U26"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="E39:F39"/>
@@ -2243,6 +2363,8 @@
     <mergeCell ref="J39:K39"/>
     <mergeCell ref="O35:P35"/>
     <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="T39:U39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
